--- a/outputs/Block6C_Final_Uncertainty_Snapshot.xlsx
+++ b/outputs/Block6C_Final_Uncertainty_Snapshot.xlsx
@@ -82,43 +82,43 @@
     <t>Monte Carlo Simulations</t>
   </si>
   <si>
-    <t>D 52.07% - R 45.01% - O 2.92%</t>
-  </si>
-  <si>
-    <t>49.74 – 53.33</t>
-  </si>
-  <si>
-    <t>43.15 – 46.74</t>
+    <t>D 52.36% - R 44.72% - O 2.92%</t>
+  </si>
+  <si>
+    <t>50.03 – 53.62</t>
+  </si>
+  <si>
+    <t>42.86 – 46.45</t>
   </si>
   <si>
     <t>1.52 – 3.52</t>
   </si>
   <si>
-    <t>D 230 / R 205</t>
-  </si>
-  <si>
-    <t>D 233.46 / R 201.54</t>
-  </si>
-  <si>
-    <t>216 – 258</t>
-  </si>
-  <si>
-    <t>177 – 219</t>
-  </si>
-  <si>
-    <t>-3 – 81</t>
-  </si>
-  <si>
-    <t>92.20%</t>
-  </si>
-  <si>
-    <t>7.80%</t>
-  </si>
-  <si>
-    <t>D 50 / R 50</t>
-  </si>
-  <si>
-    <t>D 50.08 / R 49.92</t>
+    <t>D 232 / R 203</t>
+  </si>
+  <si>
+    <t>D 236.07 / R 198.93</t>
+  </si>
+  <si>
+    <t>218 – 261</t>
+  </si>
+  <si>
+    <t>174 – 217</t>
+  </si>
+  <si>
+    <t>1 – 87</t>
+  </si>
+  <si>
+    <t>95.27%</t>
+  </si>
+  <si>
+    <t>4.73%</t>
+  </si>
+  <si>
+    <t>D 51 / R 49</t>
+  </si>
+  <si>
+    <t>D 50.22 / R 49.78</t>
   </si>
   <si>
     <t>47 – 53</t>
@@ -127,13 +127,13 @@
     <t>-6 – 6</t>
   </si>
   <si>
-    <t>43.04%</t>
-  </si>
-  <si>
-    <t>56.96%</t>
-  </si>
-  <si>
-    <t>20.17%</t>
+    <t>46.68%</t>
+  </si>
+  <si>
+    <t>53.32%</t>
+  </si>
+  <si>
+    <t>18.72%</t>
   </si>
 </sst>
 </file>

--- a/outputs/Block6C_Final_Uncertainty_Snapshot.xlsx
+++ b/outputs/Block6C_Final_Uncertainty_Snapshot.xlsx
@@ -97,7 +97,7 @@
     <t>D 232 / R 203</t>
   </si>
   <si>
-    <t>D 236.07 / R 198.93</t>
+    <t>D 236.35 / R 198.65</t>
   </si>
   <si>
     <t>218 – 261</t>
@@ -109,10 +109,10 @@
     <t>1 – 87</t>
   </si>
   <si>
-    <t>95.27%</t>
-  </si>
-  <si>
-    <t>4.73%</t>
+    <t>95.48%</t>
+  </si>
+  <si>
+    <t>4.52%</t>
   </si>
   <si>
     <t>D 51 / R 49</t>

--- a/outputs/Block6C_Final_Uncertainty_Snapshot.xlsx
+++ b/outputs/Block6C_Final_Uncertainty_Snapshot.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>Metric</t>
   </si>
@@ -82,58 +82,61 @@
     <t>Monte Carlo Simulations</t>
   </si>
   <si>
-    <t>D 52.36% - R 44.72% - O 2.92%</t>
-  </si>
-  <si>
-    <t>50.03 – 53.62</t>
-  </si>
-  <si>
-    <t>42.86 – 46.45</t>
+    <t>D 52.78% - R 44.30% - O 2.92%</t>
+  </si>
+  <si>
+    <t>50.45 – 54.05</t>
+  </si>
+  <si>
+    <t>42.43 – 46.03</t>
   </si>
   <si>
     <t>1.52 – 3.52</t>
   </si>
   <si>
-    <t>D 232 / R 203</t>
-  </si>
-  <si>
-    <t>D 236.35 / R 198.65</t>
-  </si>
-  <si>
-    <t>218 – 261</t>
-  </si>
-  <si>
-    <t>174 – 217</t>
-  </si>
-  <si>
-    <t>1 – 87</t>
-  </si>
-  <si>
-    <t>95.48%</t>
-  </si>
-  <si>
-    <t>4.52%</t>
-  </si>
-  <si>
-    <t>D 51 / R 49</t>
-  </si>
-  <si>
-    <t>D 50.22 / R 49.78</t>
-  </si>
-  <si>
-    <t>47 – 53</t>
-  </si>
-  <si>
-    <t>-6 – 6</t>
-  </si>
-  <si>
-    <t>46.68%</t>
-  </si>
-  <si>
-    <t>53.32%</t>
-  </si>
-  <si>
-    <t>18.72%</t>
+    <t>D 230 / R 205</t>
+  </si>
+  <si>
+    <t>D 239.32 / R 195.68</t>
+  </si>
+  <si>
+    <t>215 – 273</t>
+  </si>
+  <si>
+    <t>162 – 220</t>
+  </si>
+  <si>
+    <t>-5 – 111</t>
+  </si>
+  <si>
+    <t>92.50%</t>
+  </si>
+  <si>
+    <t>7.50%</t>
+  </si>
+  <si>
+    <t>D 52 / R 48</t>
+  </si>
+  <si>
+    <t>D 51.85 / R 48.15</t>
+  </si>
+  <si>
+    <t>48 – 56</t>
+  </si>
+  <si>
+    <t>44 – 52</t>
+  </si>
+  <si>
+    <t>-4 – 12</t>
+  </si>
+  <si>
+    <t>71.96%</t>
+  </si>
+  <si>
+    <t>28.04%</t>
+  </si>
+  <si>
+    <t>11.87%</t>
   </si>
 </sst>
 </file>
@@ -619,7 +622,7 @@
         <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -627,7 +630,7 @@
         <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -635,7 +638,7 @@
         <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -643,7 +646,7 @@
         <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -651,7 +654,7 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:2">

--- a/outputs/Block6C_Final_Uncertainty_Snapshot.xlsx
+++ b/outputs/Block6C_Final_Uncertainty_Snapshot.xlsx
@@ -97,7 +97,7 @@
     <t>D 230 / R 205</t>
   </si>
   <si>
-    <t>D 239.32 / R 195.68</t>
+    <t>D 239.33 / R 195.67</t>
   </si>
   <si>
     <t>215 – 273</t>

--- a/outputs/Block6C_Final_Uncertainty_Snapshot.xlsx
+++ b/outputs/Block6C_Final_Uncertainty_Snapshot.xlsx
@@ -97,7 +97,7 @@
     <t>D 230 / R 205</t>
   </si>
   <si>
-    <t>D 239.33 / R 195.67</t>
+    <t>D 239.32 / R 195.68</t>
   </si>
   <si>
     <t>215 – 273</t>

--- a/outputs/Block6C_Final_Uncertainty_Snapshot.xlsx
+++ b/outputs/Block6C_Final_Uncertainty_Snapshot.xlsx
@@ -109,10 +109,10 @@
     <t>-5 – 111</t>
   </si>
   <si>
-    <t>92.50%</t>
-  </si>
-  <si>
-    <t>7.50%</t>
+    <t>92.49%</t>
+  </si>
+  <si>
+    <t>7.51%</t>
   </si>
   <si>
     <t>D 52 / R 48</t>

--- a/outputs/Block6C_Final_Uncertainty_Snapshot.xlsx
+++ b/outputs/Block6C_Final_Uncertainty_Snapshot.xlsx
@@ -82,43 +82,43 @@
     <t>Monte Carlo Simulations</t>
   </si>
   <si>
-    <t>D 52.78% - R 44.30% - O 2.92%</t>
-  </si>
-  <si>
-    <t>50.45 – 54.05</t>
-  </si>
-  <si>
-    <t>42.43 – 46.03</t>
+    <t>D 52.77% - R 44.31% - O 2.92%</t>
+  </si>
+  <si>
+    <t>50.44 – 54.04</t>
+  </si>
+  <si>
+    <t>42.44 – 46.04</t>
   </si>
   <si>
     <t>1.52 – 3.52</t>
   </si>
   <si>
-    <t>D 230 / R 205</t>
-  </si>
-  <si>
-    <t>D 239.33 / R 195.67</t>
-  </si>
-  <si>
-    <t>215 – 273</t>
-  </si>
-  <si>
-    <t>162 – 220</t>
-  </si>
-  <si>
-    <t>-5 – 111</t>
-  </si>
-  <si>
-    <t>92.49%</t>
-  </si>
-  <si>
-    <t>7.51%</t>
+    <t>D 232 / R 203</t>
+  </si>
+  <si>
+    <t>D 240.77 / R 194.23</t>
+  </si>
+  <si>
+    <t>216 – 275</t>
+  </si>
+  <si>
+    <t>160 – 219</t>
+  </si>
+  <si>
+    <t>-3 – 115</t>
+  </si>
+  <si>
+    <t>93.45%</t>
+  </si>
+  <si>
+    <t>6.55%</t>
   </si>
   <si>
     <t>D 52 / R 48</t>
   </si>
   <si>
-    <t>D 51.85 / R 48.15</t>
+    <t>D 51.95 / R 48.05</t>
   </si>
   <si>
     <t>48 – 56</t>
@@ -130,13 +130,13 @@
     <t>-4 – 12</t>
   </si>
   <si>
-    <t>71.96%</t>
-  </si>
-  <si>
-    <t>28.04%</t>
-  </si>
-  <si>
-    <t>11.87%</t>
+    <t>74.08%</t>
+  </si>
+  <si>
+    <t>25.92%</t>
+  </si>
+  <si>
+    <t>11.59%</t>
   </si>
 </sst>
 </file>

--- a/outputs/Block6C_Final_Uncertainty_Snapshot.xlsx
+++ b/outputs/Block6C_Final_Uncertainty_Snapshot.xlsx
@@ -82,13 +82,13 @@
     <t>Monte Carlo Simulations</t>
   </si>
   <si>
-    <t>D 52.77% - R 44.31% - O 2.92%</t>
-  </si>
-  <si>
-    <t>50.44 – 54.04</t>
-  </si>
-  <si>
-    <t>42.44 – 46.04</t>
+    <t>D 52.64% - R 44.44% - O 2.92%</t>
+  </si>
+  <si>
+    <t>50.31 – 53.91</t>
+  </si>
+  <si>
+    <t>42.57 – 46.17</t>
   </si>
   <si>
     <t>1.52 – 3.52</t>
@@ -97,28 +97,28 @@
     <t>D 232 / R 203</t>
   </si>
   <si>
-    <t>D 240.77 / R 194.23</t>
-  </si>
-  <si>
-    <t>216 – 275</t>
-  </si>
-  <si>
-    <t>160 – 219</t>
-  </si>
-  <si>
-    <t>-3 – 115</t>
-  </si>
-  <si>
-    <t>93.45%</t>
-  </si>
-  <si>
-    <t>6.55%</t>
+    <t>D 240.13 / R 194.87</t>
+  </si>
+  <si>
+    <t>216 – 274</t>
+  </si>
+  <si>
+    <t>161 – 219</t>
+  </si>
+  <si>
+    <t>-3 – 113</t>
+  </si>
+  <si>
+    <t>93.02%</t>
+  </si>
+  <si>
+    <t>6.98%</t>
   </si>
   <si>
     <t>D 52 / R 48</t>
   </si>
   <si>
-    <t>D 51.95 / R 48.05</t>
+    <t>D 52.02 / R 47.98</t>
   </si>
   <si>
     <t>48 – 56</t>
@@ -130,13 +130,13 @@
     <t>-4 – 12</t>
   </si>
   <si>
-    <t>74.08%</t>
-  </si>
-  <si>
-    <t>25.92%</t>
-  </si>
-  <si>
-    <t>11.59%</t>
+    <t>74.86%</t>
+  </si>
+  <si>
+    <t>25.14%</t>
+  </si>
+  <si>
+    <t>11.31%</t>
   </si>
 </sst>
 </file>

--- a/outputs/Block6C_Final_Uncertainty_Snapshot.xlsx
+++ b/outputs/Block6C_Final_Uncertainty_Snapshot.xlsx
@@ -97,22 +97,22 @@
     <t>D 232 / R 203</t>
   </si>
   <si>
-    <t>D 240.13 / R 194.87</t>
-  </si>
-  <si>
-    <t>216 – 274</t>
-  </si>
-  <si>
-    <t>161 – 219</t>
-  </si>
-  <si>
-    <t>-3 – 113</t>
-  </si>
-  <si>
-    <t>93.02%</t>
-  </si>
-  <si>
-    <t>6.98%</t>
+    <t>D 240.65 / R 194.35</t>
+  </si>
+  <si>
+    <t>216 – 275</t>
+  </si>
+  <si>
+    <t>160 – 219</t>
+  </si>
+  <si>
+    <t>-3 – 115</t>
+  </si>
+  <si>
+    <t>93.26%</t>
+  </si>
+  <si>
+    <t>6.74%</t>
   </si>
   <si>
     <t>D 52 / R 48</t>

--- a/outputs/Block6C_Final_Uncertainty_Snapshot.xlsx
+++ b/outputs/Block6C_Final_Uncertainty_Snapshot.xlsx
@@ -82,13 +82,13 @@
     <t>Monte Carlo Simulations</t>
   </si>
   <si>
-    <t>D 52.64% - R 44.44% - O 2.92%</t>
-  </si>
-  <si>
-    <t>50.31 – 53.91</t>
-  </si>
-  <si>
-    <t>42.57 – 46.17</t>
+    <t>D 52.96% - R 44.12% - O 2.92%</t>
+  </si>
+  <si>
+    <t>50.63 – 54.22</t>
+  </si>
+  <si>
+    <t>42.26 – 45.85</t>
   </si>
   <si>
     <t>1.52 – 3.52</t>
@@ -97,28 +97,28 @@
     <t>D 232 / R 203</t>
   </si>
   <si>
-    <t>D 240.65 / R 194.35</t>
-  </si>
-  <si>
-    <t>216 – 275</t>
-  </si>
-  <si>
-    <t>160 – 219</t>
-  </si>
-  <si>
-    <t>-3 – 115</t>
-  </si>
-  <si>
-    <t>93.26%</t>
-  </si>
-  <si>
-    <t>6.74%</t>
+    <t>D 242.09 / R 192.91</t>
+  </si>
+  <si>
+    <t>217 – 277</t>
+  </si>
+  <si>
+    <t>158 – 218</t>
+  </si>
+  <si>
+    <t>-1 – 119</t>
+  </si>
+  <si>
+    <t>94.13%</t>
+  </si>
+  <si>
+    <t>5.87%</t>
   </si>
   <si>
     <t>D 52 / R 48</t>
   </si>
   <si>
-    <t>D 52.02 / R 47.98</t>
+    <t>D 52.12 / R 47.88</t>
   </si>
   <si>
     <t>48 – 56</t>
@@ -130,13 +130,13 @@
     <t>-4 – 12</t>
   </si>
   <si>
-    <t>74.86%</t>
-  </si>
-  <si>
-    <t>25.14%</t>
-  </si>
-  <si>
-    <t>11.31%</t>
+    <t>75.44%</t>
+  </si>
+  <si>
+    <t>24.56%</t>
+  </si>
+  <si>
+    <t>10.67%</t>
   </si>
 </sst>
 </file>

--- a/outputs/Block6C_Final_Uncertainty_Snapshot.xlsx
+++ b/outputs/Block6C_Final_Uncertainty_Snapshot.xlsx
@@ -118,7 +118,7 @@
     <t>D 52 / R 48</t>
   </si>
   <si>
-    <t>D 52.12 / R 47.88</t>
+    <t>D 52.17 / R 47.83</t>
   </si>
   <si>
     <t>48 – 56</t>
@@ -130,13 +130,13 @@
     <t>-4 – 12</t>
   </si>
   <si>
-    <t>75.44%</t>
-  </si>
-  <si>
-    <t>24.56%</t>
-  </si>
-  <si>
-    <t>10.67%</t>
+    <t>75.99%</t>
+  </si>
+  <si>
+    <t>24.01%</t>
+  </si>
+  <si>
+    <t>10.42%</t>
   </si>
 </sst>
 </file>

--- a/outputs/Block6C_Final_Uncertainty_Snapshot.xlsx
+++ b/outputs/Block6C_Final_Uncertainty_Snapshot.xlsx
@@ -82,22 +82,22 @@
     <t>Monte Carlo Simulations</t>
   </si>
   <si>
-    <t>D 52.96% - R 44.12% - O 2.92%</t>
-  </si>
-  <si>
-    <t>50.63 – 54.22</t>
-  </si>
-  <si>
-    <t>42.26 – 45.85</t>
+    <t>D 52.80% - R 44.28% - O 2.92%</t>
+  </si>
+  <si>
+    <t>50.48 – 54.07</t>
+  </si>
+  <si>
+    <t>42.41 – 46.00</t>
   </si>
   <si>
     <t>1.52 – 3.52</t>
   </si>
   <si>
-    <t>D 232 / R 203</t>
-  </si>
-  <si>
-    <t>D 242.09 / R 192.91</t>
+    <t>D 235 / R 200</t>
+  </si>
+  <si>
+    <t>D 243.08 / R 191.92</t>
   </si>
   <si>
     <t>217 – 277</t>
@@ -109,34 +109,34 @@
     <t>-1 – 119</t>
   </si>
   <si>
-    <t>94.13%</t>
-  </si>
-  <si>
-    <t>5.87%</t>
+    <t>94.98%</t>
+  </si>
+  <si>
+    <t>5.02%</t>
   </si>
   <si>
     <t>D 52 / R 48</t>
   </si>
   <si>
-    <t>D 52.17 / R 47.83</t>
-  </si>
-  <si>
-    <t>48 – 56</t>
-  </si>
-  <si>
-    <t>44 – 52</t>
-  </si>
-  <si>
-    <t>-4 – 12</t>
-  </si>
-  <si>
-    <t>75.99%</t>
-  </si>
-  <si>
-    <t>24.01%</t>
-  </si>
-  <si>
-    <t>10.42%</t>
+    <t>D 51.41 / R 48.59</t>
+  </si>
+  <si>
+    <t>47 – 55</t>
+  </si>
+  <si>
+    <t>45 – 53</t>
+  </si>
+  <si>
+    <t>-6 – 10</t>
+  </si>
+  <si>
+    <t>65.37%</t>
+  </si>
+  <si>
+    <t>34.63%</t>
+  </si>
+  <si>
+    <t>12.88%</t>
   </si>
 </sst>
 </file>
